--- a/archivos/formularios/formulario2_ZS.xlsx
+++ b/archivos/formularios/formulario2_ZS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://orgmas-my.sharepoint.com/personal/m_mora_organizacionmas_com/Documents/Escritorio/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m.mora\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="124" documentId="13_ncr:1_{8F8C1B8E-DF4D-4F2E-8EF0-16E08840C189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1B7A2D4D-7A35-48F9-9361-A3DC2F2435E7}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33D5C7C4-61A5-4772-B9C4-A19773CE900C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-30828" yWindow="-4452" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -1183,32 +1183,113 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="distributed" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1305,87 +1386,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1403,10 +1403,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1688,64 +1684,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="51"/>
-      <c r="B1" s="52"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="59"/>
-      <c r="G1" s="59"/>
-      <c r="H1" s="60"/>
-      <c r="I1" s="61"/>
+      <c r="A1" s="78"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="86"/>
+      <c r="F1" s="86"/>
+      <c r="G1" s="86"/>
+      <c r="H1" s="87"/>
+      <c r="I1" s="88"/>
       <c r="J1" s="18"/>
     </row>
     <row r="2" spans="1:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="54"/>
-      <c r="B2" s="46"/>
-      <c r="C2" s="55"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="82"/>
       <c r="D2" s="9"/>
-      <c r="E2" s="77" t="s">
+      <c r="E2" s="104" t="s">
         <v>46</v>
       </c>
-      <c r="F2" s="78"/>
+      <c r="F2" s="105"/>
       <c r="G2" s="9"/>
-      <c r="H2" s="62" t="s">
+      <c r="H2" s="89" t="s">
         <v>0</v>
       </c>
-      <c r="I2" s="63"/>
+      <c r="I2" s="90"/>
       <c r="J2" s="19"/>
     </row>
     <row r="3" spans="1:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="54"/>
-      <c r="B3" s="46"/>
-      <c r="C3" s="55"/>
+      <c r="A3" s="81"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="82"/>
       <c r="D3" s="9"/>
-      <c r="E3" s="79"/>
-      <c r="F3" s="80"/>
+      <c r="E3" s="106"/>
+      <c r="F3" s="107"/>
       <c r="G3" s="9"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="65"/>
+      <c r="H3" s="91"/>
+      <c r="I3" s="92"/>
       <c r="J3" s="19"/>
     </row>
     <row r="4" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="54"/>
-      <c r="B4" s="46"/>
-      <c r="C4" s="55"/>
+      <c r="A4" s="81"/>
+      <c r="B4" s="50"/>
+      <c r="C4" s="82"/>
       <c r="D4" s="9"/>
-      <c r="E4" s="79"/>
-      <c r="F4" s="80"/>
+      <c r="E4" s="106"/>
+      <c r="F4" s="107"/>
       <c r="G4" s="9"/>
-      <c r="H4" s="66"/>
-      <c r="I4" s="67"/>
+      <c r="H4" s="93"/>
+      <c r="I4" s="94"/>
       <c r="J4" s="19"/>
     </row>
     <row r="5" spans="1:10" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="54"/>
-      <c r="B5" s="46"/>
-      <c r="C5" s="55"/>
+      <c r="A5" s="81"/>
+      <c r="B5" s="50"/>
+      <c r="C5" s="82"/>
       <c r="D5" s="9"/>
-      <c r="E5" s="81"/>
-      <c r="F5" s="82"/>
+      <c r="E5" s="108"/>
+      <c r="F5" s="109"/>
       <c r="G5" s="9"/>
       <c r="H5" s="15" t="s">
         <v>19</v>
@@ -1754,9 +1750,9 @@
       <c r="J5" s="19"/>
     </row>
     <row r="6" spans="1:10" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="54"/>
-      <c r="B6" s="46"/>
-      <c r="C6" s="55"/>
+      <c r="A6" s="81"/>
+      <c r="B6" s="50"/>
+      <c r="C6" s="82"/>
       <c r="D6" s="9"/>
       <c r="E6" s="9"/>
       <c r="F6" s="9"/>
@@ -1768,31 +1764,31 @@
       <c r="J6" s="19"/>
     </row>
     <row r="7" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="54"/>
-      <c r="B7" s="46"/>
-      <c r="C7" s="55"/>
+      <c r="A7" s="81"/>
+      <c r="B7" s="50"/>
+      <c r="C7" s="82"/>
       <c r="D7" s="9"/>
       <c r="E7" s="21"/>
       <c r="F7" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="G7" s="68"/>
-      <c r="H7" s="69"/>
-      <c r="I7" s="61"/>
+      <c r="G7" s="95"/>
+      <c r="H7" s="96"/>
+      <c r="I7" s="88"/>
       <c r="J7" s="19"/>
     </row>
     <row r="8" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="56"/>
-      <c r="B8" s="57"/>
-      <c r="C8" s="58"/>
+      <c r="A8" s="83"/>
+      <c r="B8" s="84"/>
+      <c r="C8" s="85"/>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
-      <c r="F8" s="73" t="s">
+      <c r="F8" s="100" t="s">
         <v>21</v>
       </c>
-      <c r="G8" s="74"/>
-      <c r="H8" s="75"/>
-      <c r="I8" s="76"/>
+      <c r="G8" s="101"/>
+      <c r="H8" s="102"/>
+      <c r="I8" s="103"/>
       <c r="J8" s="19"/>
     </row>
     <row r="9" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1829,760 +1825,760 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="20"/>
-      <c r="B10" s="70" t="s">
+      <c r="B10" s="97" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="25"/>
       <c r="D10" s="25"/>
       <c r="E10" s="25"/>
       <c r="F10" s="25"/>
-      <c r="G10" s="46">
+      <c r="G10" s="50">
         <f>SUM((C10+C11+E10+E11)*50)</f>
         <v>0</v>
       </c>
-      <c r="H10" s="72" t="s">
+      <c r="H10" s="99" t="s">
         <v>58</v>
       </c>
-      <c r="I10" s="42"/>
-      <c r="J10" s="42"/>
+      <c r="I10" s="49"/>
+      <c r="J10" s="49"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="22"/>
-      <c r="B11" s="71"/>
+      <c r="B11" s="98"/>
       <c r="C11" s="29"/>
       <c r="D11" s="29"/>
       <c r="E11" s="29"/>
       <c r="F11" s="29"/>
-      <c r="G11" s="46"/>
-      <c r="H11" s="50"/>
-      <c r="I11" s="42"/>
-      <c r="J11" s="42"/>
+      <c r="G11" s="50"/>
+      <c r="H11" s="55"/>
+      <c r="I11" s="49"/>
+      <c r="J11" s="49"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="20"/>
-      <c r="B12" s="43" t="s">
+      <c r="B12" s="51" t="s">
         <v>8</v>
       </c>
       <c r="C12" s="25"/>
       <c r="D12" s="25"/>
       <c r="E12" s="25"/>
       <c r="F12" s="25"/>
-      <c r="G12" s="46">
+      <c r="G12" s="50">
         <f>SUM((C12+C13+E12+E13)*50)</f>
         <v>0</v>
       </c>
-      <c r="H12" s="43" t="s">
+      <c r="H12" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="I12" s="42"/>
-      <c r="J12" s="42"/>
+      <c r="I12" s="49"/>
+      <c r="J12" s="49"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="22"/>
-      <c r="B13" s="44"/>
+      <c r="B13" s="52"/>
       <c r="C13" s="29"/>
       <c r="D13" s="29"/>
       <c r="E13" s="29"/>
       <c r="F13" s="29"/>
-      <c r="G13" s="46"/>
-      <c r="H13" s="44"/>
-      <c r="I13" s="42"/>
-      <c r="J13" s="42"/>
+      <c r="G13" s="50"/>
+      <c r="H13" s="52"/>
+      <c r="I13" s="49"/>
+      <c r="J13" s="49"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="20"/>
-      <c r="B14" s="83" t="s">
+      <c r="B14" s="58" t="s">
         <v>23</v>
       </c>
       <c r="C14" s="25"/>
       <c r="D14" s="25"/>
       <c r="E14" s="25"/>
       <c r="F14" s="25"/>
-      <c r="G14" s="46">
+      <c r="G14" s="50">
         <f>SUM((C14+C15+E14+E15)*10)</f>
         <v>0</v>
       </c>
-      <c r="H14" s="49" t="s">
+      <c r="H14" s="54" t="s">
         <v>28</v>
       </c>
-      <c r="I14" s="42"/>
-      <c r="J14" s="42"/>
+      <c r="I14" s="49"/>
+      <c r="J14" s="49"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="22"/>
-      <c r="B15" s="84"/>
+      <c r="B15" s="59"/>
       <c r="C15" s="29"/>
       <c r="D15" s="29"/>
       <c r="E15" s="29"/>
       <c r="F15" s="29"/>
-      <c r="G15" s="46"/>
-      <c r="H15" s="50"/>
-      <c r="I15" s="42"/>
-      <c r="J15" s="42"/>
+      <c r="G15" s="50"/>
+      <c r="H15" s="55"/>
+      <c r="I15" s="49"/>
+      <c r="J15" s="49"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="20"/>
-      <c r="B16" s="47" t="s">
+      <c r="B16" s="57" t="s">
         <v>48</v>
       </c>
       <c r="C16" s="25"/>
       <c r="D16" s="25"/>
       <c r="E16" s="25"/>
       <c r="F16" s="25"/>
-      <c r="G16" s="46">
+      <c r="G16" s="50">
         <f t="shared" ref="G16" si="0">SUM((C16+C17+E16+E17)*50)</f>
         <v>0</v>
       </c>
-      <c r="H16" s="48" t="s">
+      <c r="H16" s="56" t="s">
         <v>29</v>
       </c>
-      <c r="I16" s="42"/>
-      <c r="J16" s="42"/>
+      <c r="I16" s="49"/>
+      <c r="J16" s="49"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="22"/>
-      <c r="B17" s="47"/>
+      <c r="B17" s="57"/>
       <c r="C17" s="29"/>
       <c r="D17" s="29"/>
       <c r="E17" s="29"/>
       <c r="F17" s="29"/>
-      <c r="G17" s="46"/>
-      <c r="H17" s="48"/>
-      <c r="I17" s="42"/>
-      <c r="J17" s="42"/>
+      <c r="G17" s="50"/>
+      <c r="H17" s="56"/>
+      <c r="I17" s="49"/>
+      <c r="J17" s="49"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="20"/>
-      <c r="B18" s="43" t="s">
+      <c r="B18" s="51" t="s">
         <v>25</v>
       </c>
       <c r="C18" s="25"/>
       <c r="D18" s="25"/>
       <c r="E18" s="25"/>
       <c r="F18" s="25"/>
-      <c r="G18" s="46">
-        <f>SUM((C18+C19+E18+E19)*2.5)</f>
+      <c r="G18" s="50">
+        <f>SUM((C18+C19+E18+E19)*50)</f>
         <v>0</v>
       </c>
-      <c r="H18" s="45" t="s">
+      <c r="H18" s="67" t="s">
         <v>30</v>
       </c>
-      <c r="I18" s="42"/>
-      <c r="J18" s="42"/>
+      <c r="I18" s="49"/>
+      <c r="J18" s="49"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="22"/>
-      <c r="B19" s="44"/>
+      <c r="B19" s="52"/>
       <c r="C19" s="29"/>
       <c r="D19" s="29"/>
       <c r="E19" s="29"/>
       <c r="F19" s="29"/>
-      <c r="G19" s="46"/>
-      <c r="H19" s="45"/>
-      <c r="I19" s="42"/>
-      <c r="J19" s="42"/>
+      <c r="G19" s="50"/>
+      <c r="H19" s="67"/>
+      <c r="I19" s="49"/>
+      <c r="J19" s="49"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="20"/>
-      <c r="B20" s="43" t="s">
+      <c r="B20" s="51" t="s">
         <v>26</v>
       </c>
       <c r="C20" s="25"/>
       <c r="D20" s="25"/>
       <c r="E20" s="25"/>
       <c r="F20" s="25"/>
-      <c r="G20" s="46">
-        <f>SUM((C20+C21+E20+E21))</f>
+      <c r="G20" s="50">
+        <f>SUM((C20+C21+E20+E21)*50)</f>
         <v>0</v>
       </c>
-      <c r="H20" s="48" t="s">
+      <c r="H20" s="56" t="s">
         <v>31</v>
       </c>
-      <c r="I20" s="42"/>
-      <c r="J20" s="42"/>
+      <c r="I20" s="49"/>
+      <c r="J20" s="49"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="22"/>
-      <c r="B21" s="44"/>
+      <c r="B21" s="52"/>
       <c r="C21" s="29"/>
       <c r="D21" s="29"/>
       <c r="E21" s="29"/>
       <c r="F21" s="29"/>
-      <c r="G21" s="46"/>
-      <c r="H21" s="48"/>
-      <c r="I21" s="42"/>
-      <c r="J21" s="42"/>
+      <c r="G21" s="50"/>
+      <c r="H21" s="56"/>
+      <c r="I21" s="49"/>
+      <c r="J21" s="49"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="20"/>
-      <c r="B22" s="43" t="s">
+      <c r="B22" s="51" t="s">
         <v>27</v>
       </c>
       <c r="C22" s="25"/>
       <c r="D22" s="25"/>
       <c r="E22" s="25"/>
       <c r="F22" s="25"/>
-      <c r="G22" s="46">
-        <f>SUM(((C22+C23+E22+E23)/2))</f>
+      <c r="G22" s="50">
+        <f>SUM(((C22+C23+E22+E23)*12.5))</f>
         <v>0</v>
       </c>
-      <c r="H22" s="43" t="s">
+      <c r="H22" s="51" t="s">
         <v>32</v>
       </c>
-      <c r="I22" s="42"/>
-      <c r="J22" s="42"/>
+      <c r="I22" s="49"/>
+      <c r="J22" s="49"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="22"/>
-      <c r="B23" s="44"/>
+      <c r="B23" s="52"/>
       <c r="C23" s="29"/>
       <c r="D23" s="29"/>
       <c r="E23" s="29"/>
       <c r="F23" s="29"/>
-      <c r="G23" s="46"/>
-      <c r="H23" s="44"/>
-      <c r="I23" s="42"/>
-      <c r="J23" s="42"/>
+      <c r="G23" s="50"/>
+      <c r="H23" s="52"/>
+      <c r="I23" s="49"/>
+      <c r="J23" s="49"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="20"/>
-      <c r="B24" s="47" t="s">
+      <c r="B24" s="57" t="s">
         <v>53</v>
       </c>
       <c r="C24" s="25"/>
       <c r="D24" s="25"/>
       <c r="E24" s="25"/>
       <c r="F24" s="25"/>
-      <c r="G24" s="46">
+      <c r="G24" s="50">
         <f>SUM((C24+C25+E24+E25)*40)</f>
         <v>0</v>
       </c>
-      <c r="H24" s="49" t="s">
+      <c r="H24" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="I24" s="42"/>
-      <c r="J24" s="42"/>
+      <c r="I24" s="49"/>
+      <c r="J24" s="49"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="B25" s="47"/>
+      <c r="B25" s="57"/>
       <c r="C25" s="29"/>
       <c r="D25" s="29"/>
       <c r="E25" s="29"/>
       <c r="F25" s="29"/>
-      <c r="G25" s="46"/>
-      <c r="H25" s="50"/>
-      <c r="I25" s="42"/>
-      <c r="J25" s="42"/>
+      <c r="G25" s="50"/>
+      <c r="H25" s="55"/>
+      <c r="I25" s="49"/>
+      <c r="J25" s="49"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="20"/>
-      <c r="B26" s="83" t="s">
+      <c r="B26" s="58" t="s">
         <v>54</v>
       </c>
       <c r="C26" s="25"/>
       <c r="D26" s="25"/>
       <c r="E26" s="25"/>
       <c r="F26" s="25"/>
-      <c r="G26" s="46">
+      <c r="G26" s="50">
         <f>SUM((C26+C27+E26+E27)*50)</f>
         <v>0</v>
       </c>
-      <c r="H26" s="49" t="s">
+      <c r="H26" s="54" t="s">
         <v>62</v>
       </c>
-      <c r="I26" s="42"/>
-      <c r="J26" s="42"/>
+      <c r="I26" s="49"/>
+      <c r="J26" s="49"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="22"/>
-      <c r="B27" s="84"/>
+      <c r="B27" s="59"/>
       <c r="C27" s="29"/>
       <c r="D27" s="29"/>
       <c r="E27" s="29"/>
       <c r="F27" s="29"/>
-      <c r="G27" s="46"/>
-      <c r="H27" s="50"/>
-      <c r="I27" s="42"/>
-      <c r="J27" s="42"/>
+      <c r="G27" s="50"/>
+      <c r="H27" s="55"/>
+      <c r="I27" s="49"/>
+      <c r="J27" s="49"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="20"/>
-      <c r="B28" s="43" t="s">
+      <c r="B28" s="51" t="s">
         <v>55</v>
       </c>
       <c r="C28" s="25"/>
       <c r="D28" s="25"/>
       <c r="E28" s="25"/>
       <c r="F28" s="25"/>
-      <c r="G28" s="46">
+      <c r="G28" s="50">
         <f>SUM((C28+C29+E28+E29)*30)</f>
         <v>0</v>
       </c>
-      <c r="H28" s="49" t="s">
+      <c r="H28" s="54" t="s">
         <v>61</v>
       </c>
-      <c r="I28" s="42"/>
-      <c r="J28" s="42"/>
+      <c r="I28" s="49"/>
+      <c r="J28" s="49"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="22"/>
-      <c r="B29" s="44"/>
+      <c r="B29" s="52"/>
       <c r="C29" s="29"/>
       <c r="D29" s="29"/>
       <c r="E29" s="29"/>
       <c r="F29" s="29"/>
-      <c r="G29" s="46"/>
-      <c r="H29" s="50"/>
-      <c r="I29" s="42"/>
-      <c r="J29" s="42"/>
+      <c r="G29" s="50"/>
+      <c r="H29" s="55"/>
+      <c r="I29" s="49"/>
+      <c r="J29" s="49"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="20"/>
-      <c r="B30" s="43" t="s">
+      <c r="B30" s="51" t="s">
         <v>56</v>
       </c>
       <c r="C30" s="25"/>
       <c r="D30" s="25"/>
       <c r="E30" s="25"/>
       <c r="F30" s="25"/>
-      <c r="G30" s="46">
+      <c r="G30" s="50">
         <f>SUM((C30+C31+E30+E31)*50)</f>
         <v>0</v>
       </c>
-      <c r="H30" s="49" t="s">
+      <c r="H30" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="I30" s="42"/>
-      <c r="J30" s="42"/>
+      <c r="I30" s="49"/>
+      <c r="J30" s="49"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="22"/>
-      <c r="B31" s="44"/>
+      <c r="B31" s="52"/>
       <c r="C31" s="29"/>
       <c r="D31" s="29"/>
       <c r="E31" s="29"/>
       <c r="F31" s="29"/>
-      <c r="G31" s="46"/>
-      <c r="H31" s="50"/>
-      <c r="I31" s="42"/>
-      <c r="J31" s="42"/>
+      <c r="G31" s="50"/>
+      <c r="H31" s="55"/>
+      <c r="I31" s="49"/>
+      <c r="J31" s="49"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="20"/>
-      <c r="B32" s="83" t="s">
+      <c r="B32" s="58" t="s">
         <v>49</v>
       </c>
       <c r="C32" s="25"/>
       <c r="D32" s="25"/>
       <c r="E32" s="25"/>
       <c r="F32" s="25"/>
-      <c r="G32" s="46">
+      <c r="G32" s="50">
         <f>SUM((C32+C33+E32+E33)*25)</f>
         <v>0</v>
       </c>
-      <c r="H32" s="48" t="s">
+      <c r="H32" s="56" t="s">
         <v>63</v>
       </c>
-      <c r="I32" s="42"/>
-      <c r="J32" s="42"/>
+      <c r="I32" s="49"/>
+      <c r="J32" s="49"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="22"/>
-      <c r="B33" s="84"/>
+      <c r="B33" s="59"/>
       <c r="C33" s="29"/>
       <c r="D33" s="29"/>
       <c r="E33" s="29"/>
       <c r="F33" s="29"/>
-      <c r="G33" s="46"/>
-      <c r="H33" s="48"/>
-      <c r="I33" s="42"/>
-      <c r="J33" s="42"/>
+      <c r="G33" s="50"/>
+      <c r="H33" s="56"/>
+      <c r="I33" s="49"/>
+      <c r="J33" s="49"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="20"/>
-      <c r="B34" s="43" t="s">
+      <c r="B34" s="51" t="s">
         <v>66</v>
       </c>
       <c r="C34" s="25"/>
       <c r="D34" s="25"/>
       <c r="E34" s="25"/>
       <c r="F34" s="25"/>
-      <c r="G34" s="46">
+      <c r="G34" s="50">
         <f>SUM(((C34+C35+E34+E35)/4)*50)</f>
         <v>0</v>
       </c>
-      <c r="H34" s="45" t="s">
+      <c r="H34" s="67" t="s">
         <v>64</v>
       </c>
-      <c r="I34" s="42"/>
-      <c r="J34" s="42"/>
+      <c r="I34" s="49"/>
+      <c r="J34" s="49"/>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="22"/>
-      <c r="B35" s="44"/>
+      <c r="B35" s="52"/>
       <c r="C35" s="29"/>
       <c r="D35" s="29"/>
       <c r="E35" s="29"/>
       <c r="F35" s="29"/>
-      <c r="G35" s="46"/>
-      <c r="H35" s="45"/>
-      <c r="I35" s="42"/>
-      <c r="J35" s="42"/>
+      <c r="G35" s="50"/>
+      <c r="H35" s="67"/>
+      <c r="I35" s="49"/>
+      <c r="J35" s="49"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="20"/>
-      <c r="B36" s="43" t="s">
+      <c r="B36" s="51" t="s">
         <v>24</v>
       </c>
       <c r="C36" s="25"/>
       <c r="D36" s="25"/>
       <c r="E36" s="25"/>
       <c r="F36" s="25"/>
-      <c r="G36" s="46">
+      <c r="G36" s="50">
         <f t="shared" ref="G36" si="1">SUM((C36+C37+E36+E37)*50)</f>
         <v>0</v>
       </c>
-      <c r="H36" s="43" t="s">
+      <c r="H36" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="I36" s="42"/>
-      <c r="J36" s="42"/>
+      <c r="I36" s="49"/>
+      <c r="J36" s="49"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="22"/>
-      <c r="B37" s="44"/>
+      <c r="B37" s="52"/>
       <c r="C37" s="29"/>
       <c r="D37" s="29"/>
       <c r="E37" s="29"/>
       <c r="F37" s="29"/>
-      <c r="G37" s="46"/>
-      <c r="H37" s="44"/>
-      <c r="I37" s="42"/>
-      <c r="J37" s="42"/>
+      <c r="G37" s="50"/>
+      <c r="H37" s="52"/>
+      <c r="I37" s="49"/>
+      <c r="J37" s="49"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="20"/>
-      <c r="B38" s="83" t="s">
+      <c r="B38" s="58" t="s">
         <v>50</v>
       </c>
       <c r="C38" s="25"/>
       <c r="D38" s="25"/>
       <c r="E38" s="25"/>
       <c r="F38" s="25"/>
-      <c r="G38" s="46">
+      <c r="G38" s="50">
         <f>SUM((C38+C39+E38+E39)*25)</f>
         <v>0</v>
       </c>
-      <c r="H38" s="43" t="s">
+      <c r="H38" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="I38" s="42"/>
-      <c r="J38" s="42"/>
+      <c r="I38" s="49"/>
+      <c r="J38" s="49"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="22"/>
-      <c r="B39" s="84"/>
+      <c r="B39" s="59"/>
       <c r="C39" s="29"/>
       <c r="D39" s="29"/>
       <c r="E39" s="29"/>
       <c r="F39" s="29"/>
-      <c r="G39" s="46"/>
-      <c r="H39" s="44"/>
-      <c r="I39" s="42"/>
-      <c r="J39" s="42"/>
+      <c r="G39" s="50"/>
+      <c r="H39" s="52"/>
+      <c r="I39" s="49"/>
+      <c r="J39" s="49"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="20"/>
-      <c r="B40" s="102" t="s">
+      <c r="B40" s="60" t="s">
         <v>57</v>
       </c>
       <c r="C40" s="25"/>
       <c r="D40" s="25"/>
       <c r="E40" s="25"/>
       <c r="F40" s="25"/>
-      <c r="G40" s="46">
+      <c r="G40" s="50">
         <f>SUM((C40+C41+E40+E41)*25)</f>
         <v>0</v>
       </c>
-      <c r="H40" s="43" t="s">
+      <c r="H40" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="I40" s="42"/>
-      <c r="J40" s="42"/>
+      <c r="I40" s="49"/>
+      <c r="J40" s="49"/>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="22"/>
-      <c r="B41" s="44"/>
+      <c r="B41" s="52"/>
       <c r="C41" s="29"/>
       <c r="D41" s="29"/>
       <c r="E41" s="29"/>
       <c r="F41" s="29"/>
-      <c r="G41" s="46"/>
-      <c r="H41" s="44"/>
-      <c r="I41" s="42"/>
-      <c r="J41" s="42"/>
+      <c r="G41" s="50"/>
+      <c r="H41" s="52"/>
+      <c r="I41" s="49"/>
+      <c r="J41" s="49"/>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="20"/>
-      <c r="B42" s="43" t="s">
+      <c r="B42" s="51" t="s">
         <v>65</v>
       </c>
       <c r="C42" s="25"/>
       <c r="D42" s="25"/>
       <c r="E42" s="25"/>
       <c r="F42" s="25"/>
-      <c r="G42" s="46">
+      <c r="G42" s="50">
         <f>SUM((C42+C43+E42+E43)*1)</f>
         <v>0</v>
       </c>
-      <c r="H42" s="43" t="s">
+      <c r="H42" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="I42" s="42"/>
-      <c r="J42" s="42"/>
+      <c r="I42" s="49"/>
+      <c r="J42" s="49"/>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="22"/>
-      <c r="B43" s="44"/>
+      <c r="B43" s="52"/>
       <c r="C43" s="29"/>
       <c r="D43" s="29"/>
       <c r="E43" s="29"/>
       <c r="F43" s="29"/>
-      <c r="G43" s="46"/>
-      <c r="H43" s="44"/>
-      <c r="I43" s="42"/>
-      <c r="J43" s="42"/>
+      <c r="G43" s="50"/>
+      <c r="H43" s="52"/>
+      <c r="I43" s="49"/>
+      <c r="J43" s="49"/>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="20"/>
-      <c r="B44" s="47" t="s">
+      <c r="B44" s="57" t="s">
         <v>43</v>
       </c>
       <c r="C44" s="25"/>
       <c r="D44" s="25"/>
       <c r="E44" s="25"/>
       <c r="F44" s="25"/>
-      <c r="G44" s="46">
+      <c r="G44" s="50">
         <f>SUM((C44+C45+E44+E45)*1)</f>
         <v>0</v>
       </c>
-      <c r="H44" s="43" t="s">
+      <c r="H44" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="I44" s="42"/>
-      <c r="J44" s="42"/>
+      <c r="I44" s="49"/>
+      <c r="J44" s="49"/>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="22"/>
-      <c r="B45" s="47"/>
+      <c r="B45" s="57"/>
       <c r="C45" s="29"/>
       <c r="D45" s="29"/>
       <c r="E45" s="29"/>
       <c r="F45" s="29"/>
-      <c r="G45" s="46"/>
-      <c r="H45" s="44"/>
-      <c r="I45" s="42"/>
-      <c r="J45" s="42"/>
+      <c r="G45" s="50"/>
+      <c r="H45" s="52"/>
+      <c r="I45" s="49"/>
+      <c r="J45" s="49"/>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="20"/>
-      <c r="B46" s="47"/>
+      <c r="B46" s="57"/>
       <c r="C46" s="25"/>
       <c r="D46" s="25"/>
       <c r="E46" s="25"/>
       <c r="F46" s="25"/>
-      <c r="G46" s="46">
+      <c r="G46" s="50">
         <f t="shared" ref="G46" si="2">SUM((C46+C47+E46+E47)*50)</f>
         <v>0</v>
       </c>
-      <c r="H46" s="43" t="s">
+      <c r="H46" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="I46" s="42"/>
-      <c r="J46" s="42"/>
+      <c r="I46" s="49"/>
+      <c r="J46" s="49"/>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="22"/>
-      <c r="B47" s="47"/>
+      <c r="B47" s="57"/>
       <c r="C47" s="29"/>
       <c r="D47" s="29"/>
       <c r="E47" s="29"/>
       <c r="F47" s="29"/>
-      <c r="G47" s="46"/>
-      <c r="H47" s="44"/>
-      <c r="I47" s="42"/>
-      <c r="J47" s="42"/>
+      <c r="G47" s="50"/>
+      <c r="H47" s="52"/>
+      <c r="I47" s="49"/>
+      <c r="J47" s="49"/>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="20"/>
-      <c r="B48" s="47"/>
+      <c r="B48" s="57"/>
       <c r="C48" s="25"/>
       <c r="D48" s="25"/>
       <c r="E48" s="25"/>
       <c r="F48" s="25"/>
-      <c r="G48" s="46">
+      <c r="G48" s="50">
         <f t="shared" ref="G48" si="3">SUM((C48+C49+E48+E49)*50)</f>
         <v>0</v>
       </c>
-      <c r="H48" s="43" t="s">
+      <c r="H48" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="I48" s="42"/>
-      <c r="J48" s="42"/>
+      <c r="I48" s="49"/>
+      <c r="J48" s="49"/>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="22"/>
-      <c r="B49" s="47"/>
+      <c r="B49" s="57"/>
       <c r="C49" s="29"/>
       <c r="D49" s="29"/>
       <c r="E49" s="29"/>
       <c r="F49" s="29"/>
-      <c r="G49" s="46"/>
-      <c r="H49" s="44"/>
-      <c r="I49" s="42"/>
-      <c r="J49" s="42"/>
+      <c r="G49" s="50"/>
+      <c r="H49" s="52"/>
+      <c r="I49" s="49"/>
+      <c r="J49" s="49"/>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="20"/>
-      <c r="B50" s="83"/>
+      <c r="B50" s="58"/>
       <c r="C50" s="25"/>
       <c r="D50" s="25"/>
       <c r="E50" s="25"/>
       <c r="F50" s="25"/>
-      <c r="G50" s="46">
+      <c r="G50" s="50">
         <f t="shared" ref="G50" si="4">SUM((C50+C51+E50+E51)*50)</f>
         <v>0</v>
       </c>
-      <c r="H50" s="49" t="s">
+      <c r="H50" s="54" t="s">
         <v>67</v>
       </c>
-      <c r="I50" s="42"/>
-      <c r="J50" s="42"/>
+      <c r="I50" s="49"/>
+      <c r="J50" s="49"/>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="22"/>
-      <c r="B51" s="84"/>
+      <c r="B51" s="59"/>
       <c r="C51" s="29"/>
       <c r="D51" s="29"/>
       <c r="E51" s="29"/>
       <c r="F51" s="29"/>
-      <c r="G51" s="46"/>
-      <c r="H51" s="50"/>
-      <c r="I51" s="42"/>
-      <c r="J51" s="42"/>
+      <c r="G51" s="50"/>
+      <c r="H51" s="55"/>
+      <c r="I51" s="49"/>
+      <c r="J51" s="49"/>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="20"/>
-      <c r="B52" s="83"/>
+      <c r="B52" s="58"/>
       <c r="C52" s="25"/>
       <c r="D52" s="25"/>
       <c r="E52" s="25"/>
       <c r="F52" s="25"/>
-      <c r="G52" s="46">
+      <c r="G52" s="50">
         <f t="shared" ref="G52" si="5">SUM((C52+C53+E52+E53)*50)</f>
         <v>0</v>
       </c>
-      <c r="H52" s="49" t="s">
+      <c r="H52" s="54" t="s">
         <v>68</v>
       </c>
-      <c r="I52" s="101"/>
-      <c r="J52" s="42"/>
+      <c r="I52" s="53"/>
+      <c r="J52" s="49"/>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="22"/>
-      <c r="B53" s="84"/>
+      <c r="B53" s="59"/>
       <c r="C53" s="29"/>
       <c r="D53" s="29"/>
       <c r="E53" s="29"/>
       <c r="F53" s="29"/>
-      <c r="G53" s="46"/>
-      <c r="H53" s="50"/>
-      <c r="I53" s="101"/>
-      <c r="J53" s="42"/>
+      <c r="G53" s="50"/>
+      <c r="H53" s="55"/>
+      <c r="I53" s="53"/>
+      <c r="J53" s="49"/>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="20"/>
-      <c r="B54" s="83"/>
+      <c r="B54" s="58"/>
       <c r="C54" s="25"/>
       <c r="D54" s="25"/>
       <c r="E54" s="25"/>
       <c r="F54" s="25"/>
-      <c r="G54" s="46">
+      <c r="G54" s="50">
         <f t="shared" ref="G54" si="6">SUM((C54+C55+E54+E55)*50)</f>
         <v>0</v>
       </c>
-      <c r="H54" s="49"/>
-      <c r="I54" s="42"/>
-      <c r="J54" s="42"/>
+      <c r="H54" s="54"/>
+      <c r="I54" s="49"/>
+      <c r="J54" s="49"/>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="22"/>
-      <c r="B55" s="84"/>
+      <c r="B55" s="59"/>
       <c r="C55" s="29"/>
       <c r="D55" s="29"/>
       <c r="E55" s="29"/>
       <c r="F55" s="29"/>
-      <c r="G55" s="46"/>
-      <c r="H55" s="50"/>
-      <c r="I55" s="42"/>
-      <c r="J55" s="42"/>
+      <c r="G55" s="50"/>
+      <c r="H55" s="55"/>
+      <c r="I55" s="49"/>
+      <c r="J55" s="49"/>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="20"/>
-      <c r="B56" s="83"/>
+      <c r="B56" s="58"/>
       <c r="C56" s="25"/>
       <c r="D56" s="25"/>
       <c r="E56" s="25"/>
       <c r="F56" s="25"/>
-      <c r="G56" s="46">
+      <c r="G56" s="50">
         <f t="shared" ref="G56" si="7">SUM((C56+C57+E56+E57)*50)</f>
         <v>0</v>
       </c>
-      <c r="H56" s="45"/>
-      <c r="I56" s="42"/>
-      <c r="J56" s="42"/>
+      <c r="H56" s="67"/>
+      <c r="I56" s="49"/>
+      <c r="J56" s="49"/>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="22"/>
-      <c r="B57" s="84"/>
+      <c r="B57" s="59"/>
       <c r="C57" s="29"/>
       <c r="D57" s="29"/>
       <c r="E57" s="29"/>
       <c r="F57" s="29"/>
-      <c r="G57" s="46"/>
-      <c r="H57" s="45"/>
-      <c r="I57" s="42"/>
-      <c r="J57" s="42"/>
+      <c r="G57" s="50"/>
+      <c r="H57" s="67"/>
+      <c r="I57" s="49"/>
+      <c r="J57" s="49"/>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="20"/>
-      <c r="B58" s="83"/>
+      <c r="B58" s="58"/>
       <c r="C58" s="25"/>
       <c r="D58" s="25"/>
       <c r="E58" s="25"/>
       <c r="F58" s="25"/>
-      <c r="G58" s="46">
+      <c r="G58" s="50">
         <f t="shared" ref="G58" si="8">SUM((C58+C59+E58+E59)*50)</f>
         <v>0</v>
       </c>
-      <c r="H58" s="48"/>
-      <c r="I58" s="101"/>
-      <c r="J58" s="42"/>
+      <c r="H58" s="56"/>
+      <c r="I58" s="53"/>
+      <c r="J58" s="49"/>
     </row>
     <row r="59" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="22"/>
-      <c r="B59" s="84"/>
+      <c r="B59" s="59"/>
       <c r="C59" s="29"/>
       <c r="D59" s="29"/>
       <c r="E59" s="29"/>
       <c r="F59" s="29"/>
-      <c r="G59" s="46"/>
-      <c r="H59" s="48"/>
-      <c r="I59" s="101"/>
-      <c r="J59" s="42"/>
+      <c r="G59" s="50"/>
+      <c r="H59" s="56"/>
+      <c r="I59" s="53"/>
+      <c r="J59" s="49"/>
     </row>
     <row r="60" spans="1:10" ht="21" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="24" t="s">
@@ -2603,7 +2599,7 @@
         <v>45</v>
       </c>
       <c r="F60" s="23">
-        <f t="shared" ref="E60:F60" si="9">(((E10+E11)*50)+((E12+E13)*50)+((E14+E15)*10)+((E18+E19)*2.5)+((E20+E21))+(((E22+E23)/2))+((E24+E25)*40)+((E26+E27)*50)+((E28+E29)*30)+((E30+E31)*50)+((E32+E33)*25)+(((E34+E35)/4)*50)+((E36+E37)*50)+((E38+E39)*25)+((E40+E41)*25)+(E42+E43)+((E16+E17)*50)+((E44+E45)*1))</f>
+        <f t="shared" ref="F60" si="9">(((E10+E11)*50)+((E12+E13)*50)+((E14+E15)*10)+((E18+E19)*2.5)+((E20+E21))+(((E22+E23)/2))+((E24+E25)*40)+((E26+E27)*50)+((E28+E29)*30)+((E30+E31)*50)+((E32+E33)*25)+(((E34+E35)/4)*50)+((E36+E37)*50)+((E38+E39)*25)+((E40+E41)*25)+(E42+E43)+((E16+E17)*50)+((E44+E45)*1))</f>
         <v>0</v>
       </c>
       <c r="G60" s="27" t="s">
@@ -2616,34 +2612,34 @@
       <c r="I60" s="28"/>
     </row>
     <row r="61" spans="1:10" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="95"/>
-      <c r="B61" s="96"/>
-      <c r="C61" s="97" t="s">
+      <c r="A61" s="61"/>
+      <c r="B61" s="62"/>
+      <c r="C61" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="D61" s="98"/>
-      <c r="E61" s="99"/>
-      <c r="F61" s="99"/>
-      <c r="G61" s="99"/>
-      <c r="H61" s="99"/>
-      <c r="I61" s="100"/>
+      <c r="D61" s="64"/>
+      <c r="E61" s="65"/>
+      <c r="F61" s="65"/>
+      <c r="G61" s="65"/>
+      <c r="H61" s="65"/>
+      <c r="I61" s="66"/>
     </row>
     <row r="62" spans="1:10" ht="90.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="6"/>
       <c r="B62" s="8"/>
-      <c r="C62" s="94">
+      <c r="C62" s="77">
         <v>1</v>
       </c>
-      <c r="D62" s="85"/>
-      <c r="E62" s="85">
+      <c r="D62" s="68"/>
+      <c r="E62" s="68">
         <v>2</v>
       </c>
-      <c r="F62" s="86"/>
+      <c r="F62" s="69"/>
       <c r="G62" s="41" t="s">
         <v>11</v>
       </c>
       <c r="H62" s="35"/>
-      <c r="I62" s="87"/>
+      <c r="I62" s="70"/>
     </row>
     <row r="63" spans="1:10" ht="108.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="11" t="s">
@@ -2653,15 +2649,15 @@
         <f>B60/H60</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="C63" s="88"/>
-      <c r="D63" s="89"/>
-      <c r="E63" s="89"/>
-      <c r="F63" s="89"/>
+      <c r="C63" s="71"/>
+      <c r="D63" s="72"/>
+      <c r="E63" s="72"/>
+      <c r="F63" s="72"/>
       <c r="G63" s="40" t="s">
         <v>13</v>
       </c>
       <c r="H63" s="7"/>
-      <c r="I63" s="87"/>
+      <c r="I63" s="70"/>
     </row>
     <row r="64" spans="1:10" ht="119.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="13" t="s">
@@ -2671,15 +2667,15 @@
         <f>(SUM(G24)/H60)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="C64" s="90"/>
-      <c r="D64" s="91"/>
-      <c r="E64" s="91"/>
-      <c r="F64" s="91"/>
+      <c r="C64" s="73"/>
+      <c r="D64" s="74"/>
+      <c r="E64" s="74"/>
+      <c r="F64" s="74"/>
       <c r="G64" s="5" t="s">
         <v>15</v>
       </c>
       <c r="H64" s="4"/>
-      <c r="I64" s="87"/>
+      <c r="I64" s="70"/>
     </row>
     <row r="65" spans="1:9" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="34" t="s">
@@ -2689,15 +2685,15 @@
         <f>(SUM(G28)/H60)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="C65" s="90"/>
-      <c r="D65" s="91"/>
-      <c r="E65" s="91"/>
-      <c r="F65" s="91"/>
+      <c r="C65" s="73"/>
+      <c r="D65" s="74"/>
+      <c r="E65" s="74"/>
+      <c r="F65" s="74"/>
       <c r="G65" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H65" s="4"/>
-      <c r="I65" s="87"/>
+      <c r="I65" s="70"/>
     </row>
     <row r="66" spans="1:9" ht="47.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="13" t="s">
@@ -2707,15 +2703,15 @@
         <f>(SUM(G26)/H60)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="C66" s="90"/>
-      <c r="D66" s="91"/>
-      <c r="E66" s="91"/>
-      <c r="F66" s="91"/>
+      <c r="C66" s="73"/>
+      <c r="D66" s="74"/>
+      <c r="E66" s="74"/>
+      <c r="F66" s="74"/>
       <c r="G66" s="38" t="s">
         <v>37</v>
       </c>
       <c r="H66" s="4"/>
-      <c r="I66" s="87"/>
+      <c r="I66" s="70"/>
     </row>
     <row r="67" spans="1:9" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="36" t="s">
@@ -2725,40 +2721,168 @@
         <f>(SUM(G32)/H60)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="C67" s="92"/>
-      <c r="D67" s="93"/>
-      <c r="E67" s="93"/>
-      <c r="F67" s="93"/>
+      <c r="C67" s="75"/>
+      <c r="D67" s="76"/>
+      <c r="E67" s="76"/>
+      <c r="F67" s="76"/>
       <c r="G67" s="38"/>
       <c r="H67" s="39"/>
-      <c r="I67" s="87"/>
+      <c r="I67" s="70"/>
     </row>
     <row r="68" spans="1:9" ht="21" x14ac:dyDescent="0.35">
-      <c r="A68" s="103" t="s">
+      <c r="A68" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="B68" s="104"/>
-      <c r="C68" s="105"/>
-      <c r="D68" s="105"/>
-      <c r="E68" s="105"/>
-      <c r="F68" s="105"/>
-      <c r="G68" s="105"/>
-      <c r="H68" s="105"/>
-      <c r="I68" s="106"/>
+      <c r="B68" s="43"/>
+      <c r="C68" s="44"/>
+      <c r="D68" s="44"/>
+      <c r="E68" s="44"/>
+      <c r="F68" s="44"/>
+      <c r="G68" s="44"/>
+      <c r="H68" s="44"/>
+      <c r="I68" s="45"/>
     </row>
     <row r="69" spans="1:9" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="107"/>
-      <c r="B69" s="108"/>
-      <c r="C69" s="108"/>
-      <c r="D69" s="108"/>
-      <c r="E69" s="108"/>
-      <c r="F69" s="108"/>
-      <c r="G69" s="108"/>
-      <c r="H69" s="108"/>
-      <c r="I69" s="109"/>
+      <c r="A69" s="46"/>
+      <c r="B69" s="47"/>
+      <c r="C69" s="47"/>
+      <c r="D69" s="47"/>
+      <c r="E69" s="47"/>
+      <c r="F69" s="47"/>
+      <c r="G69" s="47"/>
+      <c r="H69" s="47"/>
+      <c r="I69" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="152">
+    <mergeCell ref="J22:J23"/>
+    <mergeCell ref="J24:J25"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="J26:J27"/>
+    <mergeCell ref="J28:J29"/>
+    <mergeCell ref="J30:J31"/>
+    <mergeCell ref="J32:J33"/>
+    <mergeCell ref="J34:J35"/>
+    <mergeCell ref="J36:J37"/>
+    <mergeCell ref="H34:H35"/>
+    <mergeCell ref="J56:J57"/>
+    <mergeCell ref="J58:J59"/>
+    <mergeCell ref="J38:J39"/>
+    <mergeCell ref="J40:J41"/>
+    <mergeCell ref="J42:J43"/>
+    <mergeCell ref="J44:J45"/>
+    <mergeCell ref="J46:J47"/>
+    <mergeCell ref="J48:J49"/>
+    <mergeCell ref="J50:J51"/>
+    <mergeCell ref="J52:J53"/>
+    <mergeCell ref="J54:J55"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="I30:I31"/>
+    <mergeCell ref="I12:I13"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="J10:J11"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="J12:J13"/>
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="J18:J19"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="H20:H21"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="I18:I19"/>
+    <mergeCell ref="I20:I21"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="H24:H25"/>
+    <mergeCell ref="J20:J21"/>
+    <mergeCell ref="A1:C8"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="H2:I3"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="I10:I11"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="E2:F5"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="G32:G33"/>
+    <mergeCell ref="G26:G27"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="H28:H29"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="H18:H19"/>
+    <mergeCell ref="H48:H49"/>
+    <mergeCell ref="I50:I51"/>
+    <mergeCell ref="G48:G49"/>
+    <mergeCell ref="I42:I43"/>
+    <mergeCell ref="H38:H39"/>
+    <mergeCell ref="E62:F62"/>
+    <mergeCell ref="I62:I67"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="E63:F63"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="E64:F64"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="E67:F67"/>
+    <mergeCell ref="E66:F66"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="E65:F65"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="G50:G51"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="E61:I61"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="G54:G55"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="G56:G57"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="G58:G59"/>
+    <mergeCell ref="H56:H57"/>
+    <mergeCell ref="H58:H59"/>
+    <mergeCell ref="I54:I55"/>
+    <mergeCell ref="I56:I57"/>
+    <mergeCell ref="I58:I59"/>
+    <mergeCell ref="H54:H55"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="H36:H37"/>
+    <mergeCell ref="G40:G41"/>
+    <mergeCell ref="G42:G43"/>
+    <mergeCell ref="I38:I39"/>
+    <mergeCell ref="H42:H43"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="H40:H41"/>
+    <mergeCell ref="G38:G39"/>
+    <mergeCell ref="B42:B43"/>
     <mergeCell ref="A68:I68"/>
     <mergeCell ref="A69:I69"/>
     <mergeCell ref="I22:I23"/>
@@ -2783,134 +2907,6 @@
     <mergeCell ref="H30:H31"/>
     <mergeCell ref="H32:H33"/>
     <mergeCell ref="G34:G35"/>
-    <mergeCell ref="G36:G37"/>
-    <mergeCell ref="H36:H37"/>
-    <mergeCell ref="G40:G41"/>
-    <mergeCell ref="G42:G43"/>
-    <mergeCell ref="I38:I39"/>
-    <mergeCell ref="H42:H43"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="H40:H41"/>
-    <mergeCell ref="G38:G39"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="C61:D61"/>
-    <mergeCell ref="E61:I61"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="G54:G55"/>
-    <mergeCell ref="B56:B57"/>
-    <mergeCell ref="G56:G57"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="G58:G59"/>
-    <mergeCell ref="H56:H57"/>
-    <mergeCell ref="H58:H59"/>
-    <mergeCell ref="I54:I55"/>
-    <mergeCell ref="I56:I57"/>
-    <mergeCell ref="I58:I59"/>
-    <mergeCell ref="H54:H55"/>
-    <mergeCell ref="I50:I51"/>
-    <mergeCell ref="G48:G49"/>
-    <mergeCell ref="I42:I43"/>
-    <mergeCell ref="H38:H39"/>
-    <mergeCell ref="E62:F62"/>
-    <mergeCell ref="I62:I67"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="E63:F63"/>
-    <mergeCell ref="C64:D64"/>
-    <mergeCell ref="E64:F64"/>
-    <mergeCell ref="C67:D67"/>
-    <mergeCell ref="E67:F67"/>
-    <mergeCell ref="E66:F66"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="E65:F65"/>
-    <mergeCell ref="C66:D66"/>
-    <mergeCell ref="G50:G51"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="G32:G33"/>
-    <mergeCell ref="G26:G27"/>
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="H28:H29"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="B46:B47"/>
-    <mergeCell ref="H18:H19"/>
-    <mergeCell ref="H48:H49"/>
-    <mergeCell ref="A1:C8"/>
-    <mergeCell ref="D1:G1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="H2:I3"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="I10:I11"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="E2:F5"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="H12:H13"/>
-    <mergeCell ref="I30:I31"/>
-    <mergeCell ref="I12:I13"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="J10:J11"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="J12:J13"/>
-    <mergeCell ref="J14:J15"/>
-    <mergeCell ref="J16:J17"/>
-    <mergeCell ref="J18:J19"/>
-    <mergeCell ref="G20:G21"/>
-    <mergeCell ref="H20:H21"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="I18:I19"/>
-    <mergeCell ref="I20:I21"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="I16:I17"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="H24:H25"/>
-    <mergeCell ref="J20:J21"/>
-    <mergeCell ref="J56:J57"/>
-    <mergeCell ref="J58:J59"/>
-    <mergeCell ref="J38:J39"/>
-    <mergeCell ref="J40:J41"/>
-    <mergeCell ref="J42:J43"/>
-    <mergeCell ref="J44:J45"/>
-    <mergeCell ref="J46:J47"/>
-    <mergeCell ref="J48:J49"/>
-    <mergeCell ref="J50:J51"/>
-    <mergeCell ref="J52:J53"/>
-    <mergeCell ref="J54:J55"/>
-    <mergeCell ref="J22:J23"/>
-    <mergeCell ref="J24:J25"/>
-    <mergeCell ref="H22:H23"/>
-    <mergeCell ref="J26:J27"/>
-    <mergeCell ref="J28:J29"/>
-    <mergeCell ref="J30:J31"/>
-    <mergeCell ref="J32:J33"/>
-    <mergeCell ref="J34:J35"/>
-    <mergeCell ref="J36:J37"/>
-    <mergeCell ref="H34:H35"/>
   </mergeCells>
   <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
